--- a/data/seed/portfolio/L-2024-6137/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6137/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>2241000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>4216000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bekobod Plastik MChJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>371411648</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000161283343001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №231/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №85/26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -600,39 +600,39 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12054000</v>
+        <v>13192000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Namangan Moy XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>261660564</t>
+          <t>204417847</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000762519558001</t>
+          <t>20208000833262888001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №99/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №292/26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,31 +642,31 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>13092000</v>
+        <v>5927000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bekobod Plastik MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>371411648</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000161283343001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7390</t>
+          <t>Mahsulot uchun to'lov, shartnoma №51/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -683,21 +683,21 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>4089000</v>
+        <v>2941000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Shodlik Qurilish XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>266056457</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000251955828001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -707,14 +707,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №128/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №265/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,33 +722,33 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>14223000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>5098000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №12/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №2172</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>5961000</v>
+        <v>6693000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №140/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6799 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>5684000</v>
+        <v>4656000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>212417040</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000635848343001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9211 06.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №215/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -847,31 +847,31 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>2250000</v>
+        <v>4541000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №171/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №7484 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -888,31 +888,31 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>2242000</v>
+        <v>3319000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №144/26 от 06.07.2026</t>
+          <t>Предоплата за товар по дог. №163/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -927,28 +927,33 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>12599000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>1764000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Chust Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №2469</t>
+          <t>Оплата за продукцию по договору №166/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -964,22 +969,22 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13961000</v>
+        <v>5575000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Angren Sut XK</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>383719053</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000059122838001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №163/26</t>
+          <t>Оплата за транспортные услуги по договору №261/26</t>
         </is>
       </c>
     </row>
@@ -1005,39 +1010,34 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>25792000</v>
+        <v>12599000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>264710158</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000317175921001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №215/26</t>
+          <t>IYUN OYI UCHUN ISH HAQI, REESTR №41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,33 +1045,33 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>5438000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>22210000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3974 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №70/26</t>
         </is>
       </c>
     </row>
@@ -1086,23 +1086,23 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>1794000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>7727000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahor Qurilish Materiallari AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>361407682</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000228849702001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Предоплата за товар по договору №29/26 от 07.07.2026</t>
         </is>
       </c>
     </row>
@@ -1127,33 +1127,33 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>17791000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>2965000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6546</t>
+          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1169,39 +1169,39 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>25161000</v>
+        <v>1794000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Sharq Qurilish MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>261660564</t>
+          <t>334708935</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000762519558001</t>
+          <t>20208000377330009001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №29/26</t>
+          <t>Аренда помещения за июль, дог. №88/24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1211,38 +1211,38 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>6919000</v>
+        <v>12810000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9874</t>
+          <t>Оплата по счет-фактуре №9483 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1252,38 +1252,38 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>16228000</v>
+        <v>4889000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №218/26, QQS 12%</t>
+          <t>Оплата за товар по с/ф №377 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1291,40 +1291,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>4947000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>8576000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Namangan Moy XK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>204417847</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000833262888001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shartnoma №232/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №176/26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1332,33 +1332,33 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>4054000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>8071000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>367170335</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>20208000157888085001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №206/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №8223</t>
         </is>
       </c>
     </row>
@@ -1373,40 +1373,40 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>38014000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>8676000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Angren Sut XK</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>383719053</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000059122838001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №141/26, QQS bilan</t>
+          <t>Оплата за товар по с/ф №858 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1416,21 +1416,21 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>15212000</v>
+        <v>5578000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Avto Savdo AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>332180794</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000656498302001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shartnoma №66/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №7766 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1457,31 +1457,31 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>4751000</v>
+        <v>19938000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7758</t>
+          <t>Оплата за товар по счет-фактуре №2367 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1496,40 +1496,40 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>12470000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>12417000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №5/26</t>
+          <t>Предоплата за товар по дог. №5/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1539,38 +1539,38 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>2275000</v>
+        <v>1768000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bekobod Plastik MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>371411648</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000161283343001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №174/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №9465 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,35 +1578,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>1597000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6137)</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>16307000312413651417</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6137 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по счет-фактуре №9362 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1615,39 +1620,39 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>68135000</v>
+        <v>4003000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>264710158</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000317175921001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №265/26</t>
+          <t>Предоплата за материалы по дог. №116/26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1655,40 +1660,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>1718000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>1964000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Оплата за продукцию о договору №185/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1722,14 +1727,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1737,40 +1742,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>4283000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>1718000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8915</t>
+          <t>НДФЛ ЗА ИЮНЬ 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,40 +1783,35 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>2757000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>245257945</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6137)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>16307000312413651417</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6258</t>
+          <t>Kredit shartnomasi L-2024-6137 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,33 +1819,33 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>18198000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>20732000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3444</t>
+          <t>Оплата за товары согласно счет-фактуре №7132</t>
         </is>
       </c>
     </row>
@@ -1862,21 +1862,21 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>2950000</v>
+        <v>5818000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shahrisabz Meva Eksport MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>294446152</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000978840787001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №191/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №276/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
@@ -1903,38 +1903,38 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>2873000</v>
+        <v>2504000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bekobod Plastik MChJ</t>
+          <t>Chust Agro MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>371411648</t>
+          <t>303854082</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000161283343001</t>
+          <t>20208000354655098001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SHARTNOMA №234/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №230/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1942,40 +1942,40 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>72165000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>3677000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Nukus Logistik MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>367170335</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000157888085001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №36/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №43/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>5444000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>99552000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Namangan Moy XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>204417847</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000833262888001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Shartnoma №85/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №8152</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>2915000</v>
+        <v>2949000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
     </row>
@@ -2065,23 +2065,23 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>1121000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>33211000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000696262501001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за продукцию по договору №82/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,38 +2108,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>2325000</v>
+        <v>3572000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3936 24.07.2026, QQS BILAN</t>
+          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,33 +2147,33 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>7509000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>1121000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000383447242001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8516</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>6436000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>12645000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №223/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1910</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2231,38 +2231,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>8412000</v>
+        <v>2464000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Shartnoma №121/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №65/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,35 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>2246000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Chust Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за продукцию по дог. №92/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2306,23 +2311,23 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>3360000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>7086000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>319810053</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000604317579001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2332,14 +2337,14 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №230/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №255/26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2347,40 +2352,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>7209000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>75931000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Plastik AJ</t>
+          <t>Farovon Mebel AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>395539045</t>
+          <t>244615289</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000503461460001</t>
+          <t>20208000884078760001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №253/26</t>
+          <t>Оплата за продукцию по договору №243/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2388,40 +2393,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>15606000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>9823000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №244/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №88/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2430,39 +2435,34 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>3766000</v>
+        <v>300000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>330581246</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №84/26</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2470,40 +2470,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>8534000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>9199000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>264710158</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000317175921001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2076</t>
+          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2511,18 +2511,23 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>12311000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>1904000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Gulshan Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>212417040</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000635848343001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2532,14 +2537,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Оплата за продукцию по договору №191/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2549,38 +2554,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>6133000</v>
+        <v>1872000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Farovon Mebel AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>244615289</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000884078760001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9158</t>
+          <t>Оплата за товар по счет-фактуре №717 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2590,38 +2595,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>5030000</v>
+        <v>1732000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №2247 07.08.2026, QQS BILAN</t>
+          <t>Оплата по с/ф №5205 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2629,40 +2634,40 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>9434000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>10483000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Shartnoma №29/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №2153</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2672,38 +2677,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>7072000</v>
+        <v>5827000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6864 10.08.2026, QQS BILAN</t>
+          <t>Оплата за продукцию по договору №221/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2713,38 +2718,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>5207000</v>
+        <v>4352000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №74/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №7/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2754,38 +2759,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>3980000</v>
+        <v>2547000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2450 10.08.2026, QQS bilan</t>
+          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2794,39 +2799,39 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>1753000</v>
+        <v>7438000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bahor Qurilish Materiallari AJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>361407682</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000228849702001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №74/22</t>
+          <t>Tovarlar uchun to'lov h/f №2203</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2835,39 +2840,34 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>4829000</v>
+        <v>12311000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>261660564</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000762519558001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №289/26, QQS bilan</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2875,40 +2875,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>7516000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>3632000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8090</t>
+          <t>Оплата за товар по счет-фактуре №8188 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2916,40 +2916,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>10708000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>5997000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6540</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №245/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2959,38 +2959,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>3646000</v>
+        <v>8625000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Shartnoma №248/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2559</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3000,38 +3000,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>71204000</v>
+        <v>7864000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Avto Savdo AJ</t>
+          <t>Kattaqo'rg'on Agro MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>332180794</t>
+          <t>218079496</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000656498302001</t>
+          <t>20208000649830200001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2356 12.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №158/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3039,40 +3039,40 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>9747000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>5396000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Marg'ilon Savdo MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>229400144</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000787837636001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №198/26</t>
+          <t>Оплата по счет-фактуре №4625 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3080,40 +3080,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>25009000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>2924000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №196/26</t>
+          <t>ОПЛАТА ПО С/Ф №1877 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3122,39 +3122,39 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>8926000</v>
+        <v>1753000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Sharq Qurilish MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>334708935</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000377330009001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №235/26</t>
+          <t>Арендная плата за август 2026 г. по договору №88/24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,40 +3162,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>15884000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>3604000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shahrisabz Meva Eksport MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>294446152</t>
+          <t>319810053</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000978840787001</t>
+          <t>20208000604317579001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Shartnoma №76/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №552</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3205,38 +3205,38 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>5028000</v>
+        <v>36129000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №56/26 от 14.08.2026</t>
+          <t>Оплата по счет-фактуре №121 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3244,40 +3244,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>1679000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>2095000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farovon Mebel AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>244615289</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000884078760001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Предоплата за товар по дог. №225/26 от 11.08.2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3286,39 +3286,39 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>1679000</v>
+        <v>14891000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Оплата за сырье по дог. №195/26 от 11.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3327,22 +3327,22 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>7057000</v>
+        <v>30514000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Denov Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>345219100</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000655983201001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3352,14 +3352,14 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №171/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №22/26</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>15.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3368,17 +3368,22 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>17600000</v>
+        <v>20661000</v>
       </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6137)</t>
+          <t>Chust Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>16307000312413651417</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3388,14 +3393,14 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6137 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №209/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3405,38 +3410,38 @@
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>14826000</v>
+        <v>9166000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shartnoma №172/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №214/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3446,38 +3451,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>13932000</v>
+        <v>2341000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3165 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №7219 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>15.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3485,33 +3490,28 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>9044000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>245257945</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6137)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>16307000312413651417</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2024-6137 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
@@ -3528,31 +3528,31 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>4733000</v>
+        <v>16663000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shartnoma №189/26 b'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №12/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -3567,40 +3567,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>11564000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>4911000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №1/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №4984 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,40 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>3715000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>3787000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №294/26</t>
+          <t>Оплата за товар по с/ф №6372 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3651,38 +3651,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>9796000</v>
+        <v>3660000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №19/26 от 21.08.2026</t>
+          <t>Оплата по счет-фактуре №9412 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3690,40 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>26432000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>1679000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №122/26 от 24.08.2026</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3731,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>17645000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>1679000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1812 24.08.2026, QQS bilan</t>
+          <t>НДФЛ за иль 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3773,39 +3773,39 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>1096000</v>
+        <v>7618000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>319810053</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000696262501001</t>
+          <t>20208000604317579001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Оплата за сырье по дог. №213/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3813,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>2947000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>4301000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №80</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3855,22 +3855,22 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>8636000</v>
+        <v>4513000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Angren Sut XK</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>383719053</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000059122838001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3880,14 +3880,14 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №260/26</t>
+          <t>Оплата за сырье по договору №264/26 от 18.08.202, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3895,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>10488000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>15839000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №98/26</t>
+          <t>Предоплата за товар по договору №162/26 от 19.08.2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3938,38 +3938,38 @@
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>4217000</v>
+        <v>2369000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7934 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №217/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3977,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>8080000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>1775000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Angren Sut XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>383719053</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000059122838001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lo h/f №6726</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №193/26 ОТ 19.08.2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4019,22 +4019,22 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>5773000</v>
+        <v>5756000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>319810053</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000604317579001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №127/26</t>
+          <t>Оплата за сырье по дог. №129/26 от 19.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,38 +4061,38 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>5068000</v>
+        <v>6233000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6421 27.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №165 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4102,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>3951000</v>
+        <v>1777000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №129/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №29/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4141,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>31445000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>3956000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Angren Sut XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>383719053</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000059122838001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №120/26</t>
+          <t>Оплата за продукцию по дог. №280/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,35 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>3556000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2995</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4218,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>4647000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>12603000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>264710158</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000317175921001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1291</t>
+          <t>Предоплата за товар по дог. №185/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4259,40 +4264,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>4701000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1897000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №257/26</t>
+          <t>Предоплата за товар по договору №120/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4301,39 +4306,39 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>7842000</v>
+        <v>2987000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5602</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4341,40 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>2567000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>4666000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Namangan Moy XK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>204417847</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000833262888001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5205</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №22/26</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4383,22 +4388,22 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>66404000</v>
+        <v>13252000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Tong Poligraf MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>319810053</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000604317579001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4408,14 +4413,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №500</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №132/26</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4425,38 +4430,38 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>13214000</v>
+        <v>5353000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №250/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №15/26 от 25.08.2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4466,38 +4471,38 @@
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>3036000</v>
+        <v>2909000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКУРЕ №938 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата по счет-фактуре №4235 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4507,38 +4512,38 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>2485000</v>
+        <v>11336000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №255/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №1612 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4548,38 +4553,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>1793000</v>
+        <v>4498000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №108/26 от 03.09.2026</t>
+          <t>Предоплата за товар по дог. №127/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4589,38 +4594,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>1151000</v>
+        <v>3952000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8456</t>
+          <t>Оплата по счет-фактуре №8225 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4628,23 +4633,23 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>6689000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>3904000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Nukus Non XK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>284882387</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000393484042001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4654,14 +4659,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Shartnoma №287/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №236/26 от 26.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4671,38 +4676,38 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>54154000</v>
+        <v>2433000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №270/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №4350 27.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4710,40 +4715,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>7262000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>1096000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000383447242001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2198 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4751,40 +4756,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>2607000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>2795000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Shartnoma №81/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №125/26</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4792,40 +4797,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>2522000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>7504000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №245/26, QQS 12%</t>
+          <t>Оплата за товары согласно с/ф №507</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4833,40 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>2439000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>8170000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2559 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №113/26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4876,38 +4881,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>1533000</v>
+        <v>5703000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2578</t>
+          <t>Оплата по счет-фактуре №5407 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4917,38 +4922,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>1470000</v>
+        <v>5563000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Denov Polimer AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>353904555</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000346146071001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №187/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №1632 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4958,38 +4963,38 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>1446000</v>
+        <v>5285000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплаа за товар по дог. №133/26 от 07.09.2026</t>
+          <t>Оплата за продукцию по дог. №57/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4997,40 +5002,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>1825000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>4072000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bahor Qurilish Materiallari AJ</t>
+          <t>Shodlik Qurilish XK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>361407682</t>
+          <t>266056457</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000228849702001</t>
+          <t>20208000251955828001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №74/22</t>
+          <t>Оплата за продукцию по дог. №223/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5038,40 +5043,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>11073000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>2896000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №28/26</t>
+          <t>Shartnoma №237/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5080,39 +5085,34 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>11717000</v>
+        <v>300000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>330581246</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №299/26</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5121,34 +5121,39 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>12818000</v>
+        <v>61239000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Nukus Non XK</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>284882387</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000393484042001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Предоплата за материалы по дог. №277/26</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5156,40 +5161,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>31117000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>1514000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>261660564</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000762519558001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №75/26</t>
+          <t>Оплата по счет-фактуре №112 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5198,39 +5203,39 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>3413000</v>
+        <v>17196000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №112/26, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №40/26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5239,39 +5244,39 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>3221000</v>
+        <v>35930000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Marg'ilon Savdo MChJ</t>
+          <t>Denov Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>229400144</t>
+          <t>345219100</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000787837636001</t>
+          <t>20208000655983201001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3483</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №282/26</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5281,38 +5286,38 @@
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>28186000</v>
+        <v>3559000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shahrisabz Meva Eksport MChJ</t>
+          <t>Farovon Mebel AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>294446152</t>
+          <t>244615289</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000978840787001</t>
+          <t>20208000884078760001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Shartnoma №99/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №259/26 от 04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5322,21 +5327,21 @@
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>3139000</v>
+        <v>1824000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bekobod Plastik MChJ</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>371411648</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000161283343001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5346,14 +5351,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №49/26 от 11.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №760 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5363,38 +5368,38 @@
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>1246000</v>
+        <v>5588000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bekobod Plastik MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>371411648</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000161283343001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Shartnoma №8/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №2/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5404,38 +5409,38 @@
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>1140000</v>
+        <v>4323000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shahrisabz Meva Eksport MChJ</t>
+          <t>Termiz Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>294446152</t>
+          <t>271905300</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000978840787001</t>
+          <t>20208000912283828001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Shartnoma №225/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8355 07.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5443,40 +5448,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>9980000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>2088000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Nurafshon Plastik MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>261660564</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000762519558001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №223/26, QQS bilan</t>
+          <t>Оплата по с/ф №3523 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5486,21 +5491,21 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>12254000</v>
+        <v>1248000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shahrisabz Meva Eksport MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>294446152</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000978840787001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5510,14 +5515,14 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7976</t>
+          <t>Оплата за товар по счет-фактуре №3221 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5525,40 +5530,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>6481000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>1825000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Sharq Qurilish MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>334708935</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>20208000377330009001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №172/26, QQS 12%</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №88/24</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5566,40 +5571,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>2473000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>8015000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4332</t>
+          <t>Оплата за сырье по дог. №226/26 от 07.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5608,39 +5613,34 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>1748000</v>
+        <v>12818000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5648,40 +5648,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>1748000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>4248000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farovon Mebel AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>244615289</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000884078760001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Оплата по с/ф №7224 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5689,35 +5689,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>1536000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6137)</t>
+          <t>Chust Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>16307000312413651417</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6137 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за продукцию по договору №32/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,40 +5730,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>7556000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>5612000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Denov Ip-Kalava AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>345219100</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>20208000655983201001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №22/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №8283</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5767,39 +5772,39 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>4126000</v>
+        <v>20904000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8879</t>
+          <t>Предоплата за материалы по догвору №264/26</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5809,38 +5814,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>2244000</v>
+        <v>30805000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №262/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №208/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5850,38 +5855,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>1737000</v>
+        <v>2309000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №161/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9264</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5889,40 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>4931000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>1352000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>264710158</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000317175921001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №60/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №3716 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5930,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>61204000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>1924000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Angren Sut XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>383719053</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000059122838001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №6/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №27/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5973,38 +5978,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>2226000</v>
+        <v>1497000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shartnoma №129/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №198/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6014,38 +6019,38 @@
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>1780000</v>
+        <v>1265000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SHARTNOMA №193/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9309</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6053,40 +6058,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>1228000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>123796000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Namangan Moy XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>204417847</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000833262888001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №29/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5481</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6096,38 +6101,38 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>26889000</v>
+        <v>3694000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №56/26 от 15.09.2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6135,40 +6140,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>1874000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>1748000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за товар о счет-фактуре №688 от 23.09.2026, в т.ч. НДС 12%</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6177,7 +6182,7 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>3057000</v>
+        <v>1748000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
@@ -6202,14 +6207,14 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6217,40 +6222,35 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>8856000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>245257945</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6137)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>16307000312413651417</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №46/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-6137 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6260,38 +6260,38 @@
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>2820000</v>
+        <v>14610000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2671</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5426 16.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6301,38 +6301,38 @@
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>1227000</v>
+        <v>5118000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Shartnoma №15/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №91/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6340,40 +6340,40 @@
           <t>242</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
-        <v>2650000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>1815000</v>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4949</t>
+          <t>Оплата по с/ф №5667 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6381,40 +6381,40 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>3890000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>22386000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>264710158</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000317175921001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №153/26</t>
+          <t>Предоплата за товар по договору №140/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6424,38 +6424,38 @@
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>1771000</v>
+        <v>2387000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1612</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1651</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6465,38 +6465,38 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>1542000</v>
+        <v>4163000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №292/26 ОТ 25.09.2026</t>
+          <t>Shartnoma №295/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6506,38 +6506,38 @@
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>11998000</v>
+        <v>2062000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Farovon Polimer XK</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>241164871</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000128334358001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6201</t>
+          <t>Предоплата за товар по договору №166/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6547,38 +6547,38 @@
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>9524000</v>
+        <v>2203000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Jizzax Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>369186923</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000283916349001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5407</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5285</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6588,38 +6588,38 @@
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>3257000</v>
+        <v>1809000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel XK</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>375691869</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000382839163001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1879 28.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №201/26 от 22.09.2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6627,40 +6627,40 @@
           <t>249</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>2851000</v>
-      </c>
+      <c r="C159" s="2" t="n">
+        <v>3029000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6670,38 +6670,38 @@
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>2718000</v>
+        <v>2873000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Denov Polimer AJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>245257945</t>
+          <t>353904555</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000596786139001</t>
+          <t>20208000346146071001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №237/26 от 28.09.2026</t>
+          <t>Предоплата за товар по договору №171/26 от 23.09.2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6711,31 +6711,31 @@
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>1240000</v>
+        <v>10360000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ishonch Tekstil MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>360124170</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000006358483001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SHARTNOMA №165/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №3/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -6750,40 +6750,40 @@
           <t>252</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n">
-        <v>1141000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>37282000</v>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chust Agro MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>303854082</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000696262501001</t>
+          <t>20208000354655098001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7416 28.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6793,21 +6793,21 @@
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="n">
-        <v>2111000</v>
+        <v>36626000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Shahrisabz Meva Eksport MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>294446152</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000978840787001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2684</t>
+          <t>Предоплата за товар по договору №226/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6832,40 +6832,40 @@
           <t>254</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
-        <v>4443000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>5837000</v>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Savdo MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>325794555</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000678613900001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Materiallar chun oldindan to'lov, shartnoma №92/26</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2976 ОТ 28.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6874,34 +6874,39 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>300000</v>
+        <v>1141000</v>
       </c>
       <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000383447242001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>BANK XIZMATI UCHUN KOMISSIYA</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6910,58 +6915,258 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>3104000</v>
+        <v>5531000</v>
       </c>
       <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Oydin Metall Servis MChJ</t>
+          <t>Chust Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>330581246</t>
+          <t>372897211</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000257575548001</t>
+          <t>20208000947838543001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №225/26</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №169/26</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>759816000</v>
-      </c>
-      <c r="D167" s="4" t="n">
-        <v>743316000</v>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>2779000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Chust Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>325794555</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000678613900001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>5588000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Chust Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>372897211</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000947838543001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №297/26 ОТ 29.09.2026, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>23592000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Chust Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>325794555</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000678613900001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №68/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>7782000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Chust Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>325794555</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000678613900001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №4188 от 30.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Navbahor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Комиссия за перевод</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>763626000</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>747126000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C168" s="4" t="n">
+      <c r="C173" s="4" t="n">
         <v>93800000</v>
       </c>
-      <c r="D168" s="4" t="n"/>
+      <c r="D173" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
